--- a/Configs/GameConfig/Datas/map.xlsx
+++ b/Configs/GameConfig/Datas/map.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,66 @@
           <t>opponentPath</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>cellWidth</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>cellHeight</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mapCount</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>grid</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>playerEntry</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>playerStart</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>playerEnd</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>opponentEntry</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>opponentStart</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>opponentEnd</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>routeMarkers</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>enemyTypeIndex</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,96 +569,502 @@
           <t>(list#sep=;),vector2int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),(list#sep=,),string</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>vector2int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>vector2int</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>vector2int</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>vector2int</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>vector2int</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>vector2int</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),vector2int</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>格子像素宽</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>格子像素高</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>地图总数</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>列优先 grid[x][y] 格子编码 kind_lane</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>玩家入口坐标</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>玩家路径起点</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>玩家路径终点</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>对手入口坐标</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>对手路径起点</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>对手路径终点</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>表现层路径标记(含越界标记)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>本图敌人类型索引</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>网格宽</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>网格高</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>宽</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>地图索引</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>阻挡点</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>玩家路径</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>对手路径</t>
+          <t>##group</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="n">
-        <v>80</v>
-      </c>
-      <c r="C5" t="n">
-        <v>80</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>网格宽</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>网格高</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>宽</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>地图索引</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>阻挡点</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>玩家路径</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>对手路径</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>80</v>
+      </c>
+      <c r="D6" t="n">
         <v>8</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>10</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>0,8;0,7;0,6;1,6;2,6;3,6;4,6;4,5;4,4;5,4;6,4;7,4;7,5;7,6;7,7;7,8;7,9</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>7,1;7,2;7,3;6,3;5,3;4,3;3,3;3,4;3,5;2,5;1,5;0,5;0,4;0,3;0,2;0,1;0,0</t>
         </is>
+      </c>
+      <c r="J6" t="n">
+        <v>80</v>
+      </c>
+      <c r="K6" t="n">
+        <v>80</v>
+      </c>
+      <c r="L6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0_1,0_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0;2_1,2_1,2_1,2_1,2_1,0_1,0_0,2_0,2_0,2_0;2_1,2_1,2_1,2_1,2_1,0_1,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_1,0_1,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_0,0_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_0,2_0,2_0,2_0,2_0,2_0;2_1,2_1,2_1,0_1,0_0,2_0,2_0,2_0,2_0,2_0;0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,0_0,0_0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0,9</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>7,9</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>7,0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>7,1</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0,6;4,6;4,4;8,4</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>80</v>
+      </c>
+      <c r="C7" t="n">
+        <v>80</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0,8;0,7;0,6;1,6;2,6;3,6;4,6;4,5;5,5;6,5;7,5;7,6;7,7;7,8;7,9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7,1;7,2;7,3;6,3;5,3;4,3;3,3;3,4;2,4;1,4;0,4;0,3;0,2;0,1;0,0</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>80</v>
+      </c>
+      <c r="K7" t="n">
+        <v>80</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0_1,0_1,0_1,0_1,0_1,2_0,0_0,0_0,0_0,0_0;2_1,2_1,2_1,2_1,0_1,2_0,0_0,2_0,2_0,2_0;2_1,2_1,2_1,2_1,0_1,2_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_1,2_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,2_1,0_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,2_1,0_0,2_0,2_0,2_0,2_0;2_1,2_1,2_1,0_1,2_1,0_0,2_0,2_0,2_0,2_0;0_1,0_1,0_1,0_1,2_1,0_0,0_0,0_0,0_0,0_0</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0,9</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>7,9</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>7,0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>7,1</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0,5;8,5</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>80</v>
+      </c>
+      <c r="C8" t="n">
+        <v>80</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0,6;0,7;0,8;1,8;2,8;3,8;3,9;4,9;5,9;5,8;6,8;7,8;7,7;7,6;7,5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7,3;7,2;7,1;6,1;5,1;4,1;4,0;3,0;2,0;2,1;1,1;0,1;0,2;0,3;0,4</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>80</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;0_1,0_1,2_1,2_1,2_1,2_0,1_0,1_0,0_0,2_0;0_1,2_1,1_1,1_1,2_1,2_0,1_0,1_0,0_0,0_0;0_1,0_1,1_1,1_1,2_1,2_0,1_0,1_0,2_0,0_0;2_1,0_1,1_1,1_1,2_1,2_0,2_0,2_0,0_0,0_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>7,5</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>7,4</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>7,3</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0,5;8,5</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C9" t="n">
+        <v>80</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0,6;0,7;0,8;1,8;2,8;2,7;2,6;2,5;3,5;4,5;5,5;5,6;5,7;5,8;6,8;7,8;7,7;7,6;7,5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7,3;7,2;7,1;6,1;5,1;5,2;5,3;5,4;4,4;3,4;2,4;2,3;2,2;2,1;1,1;0,1;0,2;0,3;0,4</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>80</v>
+      </c>
+      <c r="K9" t="n">
+        <v>80</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;1_1,1_1,1_1,2_1,0_1,0_0,2_0,1_0,1_0,1_0;1_1,1_1,1_1,2_1,0_1,0_0,2_0,1_0,1_0,1_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0,6</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>7,5</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7,4</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>7,3</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0,5;8,5</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/map.xlsx
+++ b/Configs/GameConfig/Datas/map.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,16 @@
           <t>enemyTypeIndex</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>resourceAddress</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -629,6 +639,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -696,6 +716,16 @@
           <t>本图敌人类型索引</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>地图诊断名称，不参与战斗规则</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Unity/YooAsset 战斗地图资源地址</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -703,6 +733,16 @@
           <t>##group</t>
         </is>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -829,6 +869,16 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Map0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>BattleMap0</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -908,6 +958,16 @@
       <c r="U7" t="n">
         <v>1</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Map1</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>BattleMap0</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
@@ -987,6 +1047,16 @@
       <c r="U8" t="n">
         <v>2</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Map2</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>BattleMap0</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
@@ -1065,6 +1135,16 @@
       </c>
       <c r="U9" t="n">
         <v>3</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Map3</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>BattleMap0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/map.xlsx
+++ b/Configs/GameConfig/Datas/map.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2bb74ca99b4d4e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2eae57341abd4842"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -335,68 +335,60 @@
         <x:v>id</x:v>
       </x:c>
       <x:c r="C1" t="str">
-        <x:v>gridWidth</x:v>
+        <x:v>width</x:v>
       </x:c>
       <x:c r="D1" t="str">
-        <x:v>gridHeight</x:v>
+        <x:v>height</x:v>
       </x:c>
       <x:c r="E1" t="str">
-        <x:v>width</x:v>
+        <x:v>playerPath</x:v>
       </x:c>
       <x:c r="F1" t="str">
-        <x:v>height</x:v>
+        <x:v>opponentPath</x:v>
       </x:c>
       <x:c r="G1" t="str">
-        <x:v>blocks</x:v>
+        <x:v>cellWidth</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>playerPath</x:v>
+        <x:v>cellHeight</x:v>
       </x:c>
       <x:c r="I1" t="str">
-        <x:v>opponentPath</x:v>
+        <x:v>grid</x:v>
       </x:c>
       <x:c r="J1" t="str">
-        <x:v>cellWidth</x:v>
+        <x:v>playerEntry</x:v>
       </x:c>
       <x:c r="K1" t="str">
-        <x:v>cellHeight</x:v>
+        <x:v>playerStart</x:v>
       </x:c>
       <x:c r="L1" t="str">
-        <x:v>mapCount</x:v>
+        <x:v>playerEnd</x:v>
       </x:c>
       <x:c r="M1" t="str">
-        <x:v>grid</x:v>
+        <x:v>opponentEntry</x:v>
       </x:c>
       <x:c r="N1" t="str">
-        <x:v>playerEntry</x:v>
+        <x:v>opponentStart</x:v>
       </x:c>
       <x:c r="O1" t="str">
-        <x:v>playerStart</x:v>
+        <x:v>opponentEnd</x:v>
       </x:c>
       <x:c r="P1" t="str">
-        <x:v>playerEnd</x:v>
+        <x:v>routeMarkers</x:v>
       </x:c>
       <x:c r="Q1" t="str">
-        <x:v>opponentEntry</x:v>
+        <x:v>enemyId</x:v>
       </x:c>
       <x:c r="R1" t="str">
-        <x:v>opponentStart</x:v>
+        <x:v>name</x:v>
       </x:c>
       <x:c r="S1" t="str">
-        <x:v>opponentEnd</x:v>
-      </x:c>
-      <x:c r="T1" t="str">
-        <x:v>routeMarkers</x:v>
-      </x:c>
-      <x:c r="U1" t="str">
-        <x:v>enemyId</x:v>
-      </x:c>
-      <x:c r="V1" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="W1" t="str">
         <x:v>resourceAddress</x:v>
       </x:c>
+      <x:c r="T1"/>
+      <x:c r="U1"/>
+      <x:c r="V1"/>
+      <x:c r="W1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -412,31 +404,31 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="E2" t="str">
+        <x:v>(list#sep=;),vector2int</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>(list#sep=;),vector2int</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="H2" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="G2" t="str">
-        <x:v>string?</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>(list#sep=;),vector2int</x:v>
-      </x:c>
       <x:c r="I2" t="str">
-        <x:v>(list#sep=;),vector2int</x:v>
+        <x:v>(list#sep=;),(list#sep=,),string</x:v>
       </x:c>
       <x:c r="J2" t="str">
-        <x:v>int</x:v>
+        <x:v>vector2int</x:v>
       </x:c>
       <x:c r="K2" t="str">
-        <x:v>int</x:v>
+        <x:v>vector2int</x:v>
       </x:c>
       <x:c r="L2" t="str">
-        <x:v>int</x:v>
+        <x:v>vector2int</x:v>
       </x:c>
       <x:c r="M2" t="str">
-        <x:v>(list#sep=;),(list#sep=,),string</x:v>
+        <x:v>vector2int</x:v>
       </x:c>
       <x:c r="N2" t="str">
         <x:v>vector2int</x:v>
@@ -445,84 +437,84 @@
         <x:v>vector2int</x:v>
       </x:c>
       <x:c r="P2" t="str">
-        <x:v>vector2int</x:v>
+        <x:v>(list#sep=;),vector2int</x:v>
       </x:c>
       <x:c r="Q2" t="str">
-        <x:v>vector2int</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="R2" t="str">
-        <x:v>vector2int</x:v>
+        <x:v>string</x:v>
       </x:c>
       <x:c r="S2" t="str">
-        <x:v>vector2int</x:v>
-      </x:c>
-      <x:c r="T2" t="str">
-        <x:v>(list#sep=;),vector2int</x:v>
-      </x:c>
-      <x:c r="U2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="V2" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="W2" t="str">
-        <x:v>string</x:v>
-      </x:c>
+      <x:c r="T2"/>
+      <x:c r="U2"/>
+      <x:c r="V2"/>
+      <x:c r="W2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3"/>
-      <x:c r="E3"/>
-      <x:c r="F3"/>
-      <x:c r="G3"/>
-      <x:c r="H3"/>
-      <x:c r="I3"/>
+      <x:c r="B3" t="str">
+        <x:v>主键，地图唯一 ID，开局选地图的唯一依据</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>逻辑格子宽度（当前 8）</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>逻辑格子高度（当前 10）</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>玩家方逻辑路径，点之间分号分隔</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>对手方逻辑路径</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>像素格宽（80）</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>像素格高（80）</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>列优先 grid[x][y]，每格编码 kind_lane：kind（0道路/1可放置/2阻挡）、lane（0对手方/1玩家方）</x:v>
+      </x:c>
       <x:c r="J3" t="str">
-        <x:v>格子像素宽</x:v>
+        <x:v>玩家方地图外或边缘入口</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>格子像素高</x:v>
+        <x:v>玩家方实际路径起点格</x:v>
       </x:c>
       <x:c r="L3" t="str">
-        <x:v>地图总数</x:v>
+        <x:v>玩家方实际路径终点格</x:v>
       </x:c>
       <x:c r="M3" t="str">
-        <x:v>列优先 grid[x][y] 格子编码 kind_lane</x:v>
+        <x:v>对手方入口</x:v>
       </x:c>
       <x:c r="N3" t="str">
-        <x:v>玩家入口坐标</x:v>
+        <x:v>对手方路径起点格</x:v>
       </x:c>
       <x:c r="O3" t="str">
-        <x:v>玩家路径起点</x:v>
+        <x:v>对手方路径终点格</x:v>
       </x:c>
       <x:c r="P3" t="str">
-        <x:v>玩家路径终点</x:v>
+        <x:v>纯表现路径标记，可包含越界点，不应混进逻辑路径</x:v>
       </x:c>
       <x:c r="Q3" t="str">
-        <x:v>对手入口坐标</x:v>
+        <x:v>Normal 波未指定敌人时使用的默认敌人 ID</x:v>
       </x:c>
       <x:c r="R3" t="str">
-        <x:v>对手路径起点</x:v>
+        <x:v>诊断名称，不参与规则</x:v>
       </x:c>
       <x:c r="S3" t="str">
-        <x:v>对手路径终点</x:v>
-      </x:c>
-      <x:c r="T3" t="str">
-        <x:v>表现层路径标记(含越界标记)</x:v>
-      </x:c>
-      <x:c r="U3" t="str">
-        <x:v>本图敌人类型索引</x:v>
-      </x:c>
-      <x:c r="V3" t="str">
-        <x:v>地图诊断名称，不参与战斗规则</x:v>
-      </x:c>
-      <x:c r="W3" t="str">
-        <x:v>Unity/YooAsset 战斗地图资源地址</x:v>
-      </x:c>
+        <x:v>地图 Prefab 地址，如 BattleMap0</x:v>
+      </x:c>
+      <x:c r="T3"/>
+      <x:c r="U3"/>
+      <x:c r="V3"/>
+      <x:c r="W3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -544,45 +536,29 @@
       <x:c r="O4"/>
       <x:c r="P4"/>
       <x:c r="Q4"/>
-      <x:c r="R4"/>
-      <x:c r="S4"/>
+      <x:c r="R4" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="S4" t="str">
+        <x:v>c</x:v>
+      </x:c>
       <x:c r="T4"/>
       <x:c r="U4"/>
-      <x:c r="V4" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="W4" t="str">
-        <x:v>c</x:v>
-      </x:c>
+      <x:c r="V4"/>
+      <x:c r="W4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B5" t="str">
-        <x:v>ID(主键)</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>网格宽</x:v>
-      </x:c>
-      <x:c r="D5" t="str">
-        <x:v>网格高</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>宽</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>高</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>阻挡点</x:v>
-      </x:c>
-      <x:c r="H5" t="str">
-        <x:v>玩家路径</x:v>
-      </x:c>
-      <x:c r="I5" t="str">
-        <x:v>对手路径</x:v>
-      </x:c>
+      <x:c r="B5"/>
+      <x:c r="C5"/>
+      <x:c r="D5"/>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5"/>
       <x:c r="J5"/>
       <x:c r="K5"/>
       <x:c r="L5"/>
@@ -594,9 +570,7 @@
       <x:c r="R5"/>
       <x:c r="S5"/>
       <x:c r="T5"/>
-      <x:c r="U5" t="str">
-        <x:v>本图敌人ID</x:v>
-      </x:c>
+      <x:c r="U5"/>
       <x:c r="V5"/>
       <x:c r="W5"/>
     </x:row>
@@ -606,66 +580,60 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>0,8;0,7;0,6;1,6;2,6;3,6;4,6;4,5;4,4;5,4;6,4;7,4;7,5;7,6;7,7;7,8;7,9</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>7,1;7,2;7,3;6,3;5,3;4,3;3,3;3,4;3,5;2,5;1,5;0,5;0,4;0,3;0,2;0,1;0,0</x:v>
+      </x:c>
+      <x:c r="G6" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D6" t="n">
+      <x:c r="H6" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E6" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G6"/>
-      <x:c r="H6" t="str">
-        <x:v>0,8;0,7;0,6;1,6;2,6;3,6;4,6;4,5;4,4;5,4;6,4;7,4;7,5;7,6;7,7;7,8;7,9</x:v>
-      </x:c>
       <x:c r="I6" t="str">
-        <x:v>7,1;7,2;7,3;6,3;5,3;4,3;3,3;3,4;3,5;2,5;1,5;0,5;0,4;0,3;0,2;0,1;0,0</x:v>
-      </x:c>
-      <x:c r="J6" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K6" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="L6" t="n">
-        <x:v>4</x:v>
+        <x:v>0_1,0_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0;2_1,2_1,2_1,2_1,2_1,0_1,0_0,2_0,2_0,2_0;2_1,2_1,2_1,2_1,2_1,0_1,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_1,0_1,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_0,0_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_0,2_0,2_0,2_0,2_0,2_0;2_1,2_1,2_1,0_1,0_0,2_0,2_0,2_0,2_0,2_0;0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,0_0,0_0</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>0,9</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>0,8</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>7,9</x:v>
       </x:c>
       <x:c r="M6" t="str">
-        <x:v>0_1,0_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0;2_1,2_1,2_1,2_1,2_1,0_1,0_0,2_0,2_0,2_0;2_1,2_1,2_1,2_1,2_1,0_1,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_1,0_1,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_0,0_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_0,2_0,2_0,2_0,2_0,2_0;2_1,2_1,2_1,0_1,0_0,2_0,2_0,2_0,2_0,2_0;0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,0_0,0_0</x:v>
+        <x:v>7,0</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>0,9</x:v>
+        <x:v>7,1</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>0,8</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="P6" t="str">
-        <x:v>7,9</x:v>
-      </x:c>
-      <x:c r="Q6" t="str">
-        <x:v>7,0</x:v>
+        <x:v>0,6;4,6;4,4;8,4</x:v>
+      </x:c>
+      <x:c r="Q6" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R6" t="str">
-        <x:v>7,1</x:v>
+        <x:v>Map0</x:v>
       </x:c>
       <x:c r="S6" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="T6" t="str">
-        <x:v>0,6;4,6;4,4;8,4</x:v>
-      </x:c>
-      <x:c r="U6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V6" t="str">
-        <x:v>Map0</x:v>
-      </x:c>
-      <x:c r="W6" t="str">
         <x:v>BattleMap0</x:v>
       </x:c>
+      <x:c r="T6"/>
+      <x:c r="U6"/>
+      <x:c r="V6"/>
+      <x:c r="W6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
@@ -673,66 +641,60 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C7" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>0,8;0,7;0,6;1,6;2,6;3,6;4,6;4,5;5,5;6,5;7,5;7,6;7,7;7,8;7,9</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>7,1;7,2;7,3;6,3;5,3;4,3;3,3;3,4;2,4;1,4;0,4;0,3;0,2;0,1;0,0</x:v>
+      </x:c>
+      <x:c r="G7" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D7" t="n">
+      <x:c r="H7" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E7" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G7"/>
-      <x:c r="H7" t="str">
-        <x:v>0,8;0,7;0,6;1,6;2,6;3,6;4,6;4,5;5,5;6,5;7,5;7,6;7,7;7,8;7,9</x:v>
-      </x:c>
       <x:c r="I7" t="str">
-        <x:v>7,1;7,2;7,3;6,3;5,3;4,3;3,3;3,4;2,4;1,4;0,4;0,3;0,2;0,1;0,0</x:v>
-      </x:c>
-      <x:c r="J7" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K7" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="L7" t="n">
-        <x:v>4</x:v>
+        <x:v>0_1,0_1,0_1,0_1,0_1,2_0,0_0,0_0,0_0,0_0;2_1,2_1,2_1,2_1,0_1,2_0,0_0,2_0,2_0,2_0;2_1,2_1,2_1,2_1,0_1,2_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_1,2_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,2_1,0_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,2_1,0_0,2_0,2_0,2_0,2_0;2_1,2_1,2_1,0_1,2_1,0_0,2_0,2_0,2_0,2_0;0_1,0_1,0_1,0_1,2_1,0_0,0_0,0_0,0_0,0_0</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>0,9</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>0,8</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>7,9</x:v>
       </x:c>
       <x:c r="M7" t="str">
-        <x:v>0_1,0_1,0_1,0_1,0_1,2_0,0_0,0_0,0_0,0_0;2_1,2_1,2_1,2_1,0_1,2_0,0_0,2_0,2_0,2_0;2_1,2_1,2_1,2_1,0_1,2_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,0_1,2_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,2_1,0_0,0_0,1_0,1_0,2_0;2_1,1_1,1_1,0_1,2_1,0_0,2_0,2_0,2_0,2_0;2_1,2_1,2_1,0_1,2_1,0_0,2_0,2_0,2_0,2_0;0_1,0_1,0_1,0_1,2_1,0_0,0_0,0_0,0_0,0_0</x:v>
+        <x:v>7,0</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>0,9</x:v>
+        <x:v>7,1</x:v>
       </x:c>
       <x:c r="O7" t="str">
-        <x:v>0,8</x:v>
+        <x:v>0,0</x:v>
       </x:c>
       <x:c r="P7" t="str">
-        <x:v>7,9</x:v>
-      </x:c>
-      <x:c r="Q7" t="str">
-        <x:v>7,0</x:v>
+        <x:v>0,5;8,5</x:v>
+      </x:c>
+      <x:c r="Q7" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R7" t="str">
-        <x:v>7,1</x:v>
+        <x:v>Map1</x:v>
       </x:c>
       <x:c r="S7" t="str">
-        <x:v>0,0</x:v>
-      </x:c>
-      <x:c r="T7" t="str">
-        <x:v>0,5;8,5</x:v>
-      </x:c>
-      <x:c r="U7" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="V7" t="str">
-        <x:v>Map1</x:v>
-      </x:c>
-      <x:c r="W7" t="str">
         <x:v>BattleMap0</x:v>
       </x:c>
+      <x:c r="T7"/>
+      <x:c r="U7"/>
+      <x:c r="V7"/>
+      <x:c r="W7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
@@ -740,66 +702,60 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>0,6;0,7;0,8;1,8;2,8;3,8;3,9;4,9;5,9;5,8;6,8;7,8;7,7;7,6;7,5</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>7,3;7,2;7,1;6,1;5,1;4,1;4,0;3,0;2,0;2,1;1,1;0,1;0,2;0,3;0,4</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D8" t="n">
+      <x:c r="H8" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E8" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F8" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G8"/>
-      <x:c r="H8" t="str">
-        <x:v>0,6;0,7;0,8;1,8;2,8;3,8;3,9;4,9;5,9;5,8;6,8;7,8;7,7;7,6;7,5</x:v>
-      </x:c>
       <x:c r="I8" t="str">
-        <x:v>7,3;7,2;7,1;6,1;5,1;4,1;4,0;3,0;2,0;2,1;1,1;0,1;0,2;0,3;0,4</x:v>
-      </x:c>
-      <x:c r="J8" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K8" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="L8" t="n">
-        <x:v>4</x:v>
+        <x:v>2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;0_1,0_1,2_1,2_1,2_1,2_0,1_0,1_0,0_0,2_0;0_1,2_1,1_1,1_1,2_1,2_0,1_0,1_0,0_0,0_0;0_1,0_1,1_1,1_1,2_1,2_0,1_0,1_0,2_0,0_0;2_1,0_1,1_1,1_1,2_1,2_0,2_0,2_0,0_0,0_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>0,5</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>0,6</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>7,5</x:v>
       </x:c>
       <x:c r="M8" t="str">
-        <x:v>2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;0_1,0_1,2_1,2_1,2_1,2_0,1_0,1_0,0_0,2_0;0_1,2_1,1_1,1_1,2_1,2_0,1_0,1_0,0_0,0_0;0_1,0_1,1_1,1_1,2_1,2_0,1_0,1_0,2_0,0_0;2_1,0_1,1_1,1_1,2_1,2_0,2_0,2_0,0_0,0_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0</x:v>
+        <x:v>7,4</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>0,5</x:v>
+        <x:v>7,3</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>0,6</x:v>
+        <x:v>0,4</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>7,5</x:v>
-      </x:c>
-      <x:c r="Q8" t="str">
-        <x:v>7,4</x:v>
+        <x:v>0,5;8,5</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R8" t="str">
-        <x:v>7,3</x:v>
+        <x:v>Map2</x:v>
       </x:c>
       <x:c r="S8" t="str">
-        <x:v>0,4</x:v>
-      </x:c>
-      <x:c r="T8" t="str">
-        <x:v>0,5;8,5</x:v>
-      </x:c>
-      <x:c r="U8" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="V8" t="str">
-        <x:v>Map2</x:v>
-      </x:c>
-      <x:c r="W8" t="str">
         <x:v>BattleMap0</x:v>
       </x:c>
+      <x:c r="T8"/>
+      <x:c r="U8"/>
+      <x:c r="V8"/>
+      <x:c r="W8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
@@ -807,66 +763,60 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>0,6;0,7;0,8;1,8;2,8;2,7;2,6;2,5;3,5;4,5;5,5;5,6;5,7;5,8;6,8;7,8;7,7;7,6;7,5</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>7,3;7,2;7,1;6,1;5,1;5,2;5,3;5,4;4,4;3,4;2,4;2,3;2,2;2,1;1,1;0,1;0,2;0,3;0,4</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D9" t="n">
+      <x:c r="H9" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="E9" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G9"/>
-      <x:c r="H9" t="str">
-        <x:v>0,6;0,7;0,8;1,8;2,8;2,7;2,6;2,5;3,5;4,5;5,5;5,6;5,7;5,8;6,8;7,8;7,7;7,6;7,5</x:v>
-      </x:c>
       <x:c r="I9" t="str">
-        <x:v>7,3;7,2;7,1;6,1;5,1;5,2;5,3;5,4;4,4;3,4;2,4;2,3;2,2;2,1;1,1;0,1;0,2;0,3;0,4</x:v>
-      </x:c>
-      <x:c r="J9" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K9" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="L9" t="n">
+        <x:v>2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;1_1,1_1,1_1,2_1,0_1,0_0,2_0,1_0,1_0,1_0;1_1,1_1,1_1,2_1,0_1,0_0,2_0,1_0,1_0,1_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>0,5</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>0,6</x:v>
+      </x:c>
+      <x:c r="L9" t="str">
+        <x:v>7,5</x:v>
+      </x:c>
+      <x:c r="M9" t="str">
+        <x:v>7,4</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>7,3</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>0,4</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>0,5;8,5</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="M9" t="str">
-        <x:v>2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;1_1,1_1,1_1,2_1,0_1,0_0,2_0,1_0,1_0,1_0;1_1,1_1,1_1,2_1,0_1,0_0,2_0,1_0,1_0,1_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0;2_1,0_1,2_1,2_1,2_1,2_0,2_0,2_0,0_0,2_0;2_1,0_1,0_1,0_1,0_1,0_0,0_0,0_0,0_0,2_0</x:v>
-      </x:c>
-      <x:c r="N9" t="str">
-        <x:v>0,5</x:v>
-      </x:c>
-      <x:c r="O9" t="str">
-        <x:v>0,6</x:v>
-      </x:c>
-      <x:c r="P9" t="str">
-        <x:v>7,5</x:v>
-      </x:c>
-      <x:c r="Q9" t="str">
-        <x:v>7,4</x:v>
-      </x:c>
       <x:c r="R9" t="str">
-        <x:v>7,3</x:v>
+        <x:v>Map3</x:v>
       </x:c>
       <x:c r="S9" t="str">
-        <x:v>0,4</x:v>
-      </x:c>
-      <x:c r="T9" t="str">
-        <x:v>0,5;8,5</x:v>
-      </x:c>
-      <x:c r="U9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="V9" t="str">
-        <x:v>Map3</x:v>
-      </x:c>
-      <x:c r="W9" t="str">
         <x:v>BattleMap0</x:v>
       </x:c>
+      <x:c r="T9"/>
+      <x:c r="U9"/>
+      <x:c r="V9"/>
+      <x:c r="W9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
